--- a/etf_holdings/2026-09-09_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-09_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,97 +486,133 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3131</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>弘塑</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3.56%</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1450000</v>
+      </c>
       <c r="K2" t="n">
-        <v>91000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>1350000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+          <t>2026-09-08_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>聯發科技</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>聯發科技</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.71%</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>5.33%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5.81%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>+0.48%</t>
+        </is>
+      </c>
       <c r="J3" t="n">
-        <v>648000</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>900000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+          <t>2026-09-08_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -591,55 +627,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>旺矽科技</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>旺矽科技</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>250000</v>
+        <v>380000</v>
       </c>
       <c r="K4" t="n">
-        <v>290000</v>
+        <v>450000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+          <t>2026-09-08_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -649,114 +685,2220 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>79000</v>
+        <v>1800000</v>
       </c>
       <c r="K5" t="n">
-        <v>109000</v>
+        <v>1500000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>-300,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+          <t>2026-09-08_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5.09%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4.38%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.71%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1730020</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1500020</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-230,000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-08_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.04%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>4294000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-894,000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-08_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6.39%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5.31%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.08%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1391225</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1171225</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-220,000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-08_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15.86%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>15.59%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>10100000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-08_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>210500</v>
+      </c>
+      <c r="K10" t="n">
+        <v>140500</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-70,000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-08_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>650000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>760000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>110,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-08_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-08_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>聯華電子</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>聯華電子</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.08%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>804000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>766000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-38,000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>台灣積體電路製造</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>13.65%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>14.98%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>+1.33%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>588000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>637000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>49,000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1.92%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.43%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>97000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>80000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-17,000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>南亞科技</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>南亞科技</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>105000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>79000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-26,000</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>中國信託金融控股</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>中國信託金融控股</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.72%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>+0.34%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2178000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2652000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>474,000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>欣興電子</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>欣興電子</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.46%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>252000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>198000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-54,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>聯亞光電工業</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>聯亞光電工業</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>健策精密工業</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>健策精密工業</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>18000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>世芯電子</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>世芯電子</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>53000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>47000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>貿聯控股（BizLink Holding In</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>貿聯控股（BizLink Holding In</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>94000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>74000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>頎邦科技</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>頎邦科技</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>517000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>390000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-127,000</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>77000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>60000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-17,000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7750</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>新代科技</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>新代科技</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2.06%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>92000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>80000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-12,000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>南亞電路板</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>南亞電路板</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>125000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>102000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-23,000</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-08_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>51000</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-08_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>富喬</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>富喬</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>10877000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>11420868</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>543,868</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-08_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1590</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>亞德客-KY</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8028</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>昇陽半導體</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>168000</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>5.45%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6.20%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+0.75%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1570000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1720000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>150,000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>152000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>132000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>6531</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>愛普*</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>愛普*</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2.54%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3.44%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>+0.90%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>750000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>950000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>00407A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>91000</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>648000</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>290000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>+0.50%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>79000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>109000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>6669</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>3.92%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>-0.84%</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J42" t="n">
         <v>491644</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K42" t="n">
         <v>421644</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-70,000</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>2026-09-08_00407A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-09_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-09_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -942,55 +942,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>15.86%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15.59%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10100000</v>
+        <v>804000</v>
       </c>
       <c r="K9" t="n">
-        <v>10000000</v>
+        <v>766000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>-38,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-08_00403A_full_holdings.xlsx</t>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1000,60 +1000,60 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>台灣積體電路製造</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>台灣積體電路製造</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>13.65%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>14.98%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>210500</v>
+        <v>588000</v>
       </c>
       <c r="K10" t="n">
-        <v>140500</v>
+        <v>637000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-70,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-08_00403A_full_holdings.xlsx</t>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1063,60 +1063,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>650000</v>
+        <v>97000</v>
       </c>
       <c r="K11" t="n">
-        <v>760000</v>
+        <v>80000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>110,000</t>
+          <t>-17,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-08_00403A_full_holdings.xlsx</t>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1131,48 +1131,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>400000</v>
+        <v>105000</v>
       </c>
       <c r="K12" t="n">
-        <v>200000</v>
+        <v>79000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-200,000</t>
+          <t>-26,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-08_00403A_full_holdings.xlsx</t>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1189,48 +1189,48 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>804000</v>
+        <v>2178000</v>
       </c>
       <c r="K13" t="n">
-        <v>766000</v>
+        <v>2652000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-38,000</t>
+          <t>474,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1252,48 +1252,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>台灣積體電路製造</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>台灣積體電路製造</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.65%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14.98%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>588000</v>
+        <v>252000</v>
       </c>
       <c r="K14" t="n">
-        <v>637000</v>
+        <v>198000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>-54,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1320,43 +1320,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>97000</v>
+        <v>22000</v>
       </c>
       <c r="K15" t="n">
-        <v>80000</v>
+        <v>17000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-17,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1383,43 +1383,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>105000</v>
+        <v>18000</v>
       </c>
       <c r="K16" t="n">
-        <v>79000</v>
+        <v>13000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-26,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1441,48 +1441,48 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>世芯電子</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>世芯電子</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2178000</v>
+        <v>53000</v>
       </c>
       <c r="K17" t="n">
-        <v>2652000</v>
+        <v>47000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>474,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1509,43 +1509,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>252000</v>
+        <v>94000</v>
       </c>
       <c r="K18" t="n">
-        <v>198000</v>
+        <v>74000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-54,000</t>
+          <t>-20,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1572,43 +1572,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>頎邦科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>頎邦科技</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>22000</v>
+        <v>517000</v>
       </c>
       <c r="K19" t="n">
-        <v>17000</v>
+        <v>390000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>-127,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1635,43 +1635,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>18000</v>
+        <v>77000</v>
       </c>
       <c r="K20" t="n">
-        <v>13000</v>
+        <v>60000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>-17,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1698,43 +1698,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>世芯電子</t>
+          <t>新代科技</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>世芯電子</t>
+          <t>新代科技</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>53000</v>
+        <v>92000</v>
       </c>
       <c r="K21" t="n">
-        <v>47000</v>
+        <v>80000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>-12,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1761,43 +1761,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>南亞電路板</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>南亞電路板</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>94000</v>
+        <v>125000</v>
       </c>
       <c r="K22" t="n">
-        <v>74000</v>
+        <v>102000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>-23,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1809,133 +1809,97 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6147</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>頎邦科技</t>
-        </is>
-      </c>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0.93%</t>
-        </is>
-      </c>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>517000</v>
-      </c>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>390000</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-127,000</t>
-        </is>
-      </c>
+        <v>250000</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+          <t>2026-09-08_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>77000</v>
-      </c>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>60000</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-17,000</t>
-        </is>
-      </c>
+        <v>51000</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+          <t>2026-09-08_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1945,269 +1909,233 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>92000</v>
+        <v>10877000</v>
       </c>
       <c r="K25" t="n">
-        <v>80000</v>
+        <v>11420868</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-12,000</t>
+          <t>543,868</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+          <t>2026-09-08_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>南亞電路板</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>南亞電路板</t>
-        </is>
-      </c>
+          <t>亞德客-KY</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.24%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>102000</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>-23,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.38%</t>
-        </is>
-      </c>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>250000</v>
-      </c>
+      <c r="J27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-08_00992A_full_holdings.xlsx</t>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0.89%</t>
-        </is>
-      </c>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>51000</v>
-      </c>
+      <c r="J28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-08_00992A_full_holdings.xlsx</t>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>富喬</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>富喬</t>
-        </is>
-      </c>
+          <t>昇陽半導體</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3.57%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>3.46%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-0.11%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>10877000</v>
-      </c>
-      <c r="K29" t="n">
-        <v>11420868</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>543,868</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-08_00992A_full_holdings.xlsx</t>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2229,24 +2157,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>1000</v>
+        <v>168000</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2264,37 +2192,55 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+          <t>5.45%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6.20%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>+0.75%</t>
+        </is>
+      </c>
       <c r="J31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+        <v>1570000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1720000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>150,000</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>2026-09-08_00405A_full_holdings.xlsx</t>
@@ -2309,37 +2255,55 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
       <c r="J32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+        <v>152000</v>
+      </c>
+      <c r="K32" t="n">
+        <v>132000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>2026-09-08_00405A_full_holdings.xlsx</t>
@@ -2354,37 +2318,55 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>愛普*</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>愛普*</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+          <t>2.54%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3.44%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>+0.90%</t>
+        </is>
+      </c>
       <c r="J33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+        <v>750000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>950000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>2026-09-08_00405A_full_holdings.xlsx</t>
@@ -2394,115 +2376,97 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>勤誠</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.55%</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>168000</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>91000</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>5.45%</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>6.20%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>+0.75%</t>
-        </is>
-      </c>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>1570000</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1720000</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>150,000</t>
-        </is>
-      </c>
+        <v>648000</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2512,60 +2476,60 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>152000</v>
+        <v>250000</v>
       </c>
       <c r="K36" t="n">
-        <v>132000</v>
+        <v>290000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2580,48 +2544,48 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>+0.90%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>750000</v>
+        <v>79000</v>
       </c>
       <c r="K37" t="n">
-        <v>950000</v>
+        <v>109000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2633,272 +2597,56 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3131</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>弘塑</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4.76%</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>3.92%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-0.84%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>491644</v>
+      </c>
       <c r="K38" t="n">
-        <v>91000</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
+        <v>421644</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-70,000</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>1.71%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
-        <v>648000</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1.33%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>1.60%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>+0.27%</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>250000</v>
-      </c>
-      <c r="K40" t="n">
-        <v>290000</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1.07%</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>1.57%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>+0.50%</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>79000</v>
-      </c>
-      <c r="K41" t="n">
-        <v>109000</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>4.76%</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>3.92%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>-0.84%</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>491644</v>
-      </c>
-      <c r="K42" t="n">
-        <v>421644</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>-70,000</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
         <is>
           <t>2026-09-08_00407A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-09_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-09_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -942,55 +942,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>15.86%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>15.59%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>804000</v>
+        <v>10100000</v>
       </c>
       <c r="K9" t="n">
-        <v>766000</v>
+        <v>10000000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-38,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+          <t>2026-09-08_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1000,60 +1000,60 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>台灣積體電路製造</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>台灣積體電路製造</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13.65%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14.98%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>588000</v>
+        <v>210500</v>
       </c>
       <c r="K10" t="n">
-        <v>637000</v>
+        <v>140500</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>-70,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+          <t>2026-09-08_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1063,60 +1063,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>97000</v>
+        <v>650000</v>
       </c>
       <c r="K11" t="n">
-        <v>80000</v>
+        <v>760000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-17,000</t>
+          <t>110,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+          <t>2026-09-08_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1131,48 +1131,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>105000</v>
+        <v>400000</v>
       </c>
       <c r="K12" t="n">
-        <v>79000</v>
+        <v>200000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-26,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-08_00985A_full_holdings.xlsx</t>
+          <t>2026-09-08_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1189,48 +1189,48 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2178000</v>
+        <v>804000</v>
       </c>
       <c r="K13" t="n">
-        <v>2652000</v>
+        <v>766000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>474,000</t>
+          <t>-38,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1252,48 +1252,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>台灣積體電路製造</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>台灣積體電路製造</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>13.65%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>14.98%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>252000</v>
+        <v>588000</v>
       </c>
       <c r="K14" t="n">
-        <v>198000</v>
+        <v>637000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-54,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1320,43 +1320,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>22000</v>
+        <v>97000</v>
       </c>
       <c r="K15" t="n">
-        <v>17000</v>
+        <v>80000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>-17,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1383,43 +1383,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18000</v>
+        <v>105000</v>
       </c>
       <c r="K16" t="n">
-        <v>13000</v>
+        <v>79000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>-26,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1441,48 +1441,48 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>世芯電子</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>世芯電子</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>53000</v>
+        <v>2178000</v>
       </c>
       <c r="K17" t="n">
-        <v>47000</v>
+        <v>2652000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>474,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1509,43 +1509,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>94000</v>
+        <v>252000</v>
       </c>
       <c r="K18" t="n">
-        <v>74000</v>
+        <v>198000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>-54,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1572,43 +1572,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>517000</v>
+        <v>22000</v>
       </c>
       <c r="K19" t="n">
-        <v>390000</v>
+        <v>17000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-127,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1635,43 +1635,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>77000</v>
+        <v>18000</v>
       </c>
       <c r="K20" t="n">
-        <v>60000</v>
+        <v>13000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-17,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1698,43 +1698,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>世芯電子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>世芯電子</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>92000</v>
+        <v>53000</v>
       </c>
       <c r="K21" t="n">
-        <v>80000</v>
+        <v>47000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-12,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1761,43 +1761,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>南亞電路板</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>南亞電路板</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>125000</v>
+        <v>94000</v>
       </c>
       <c r="K22" t="n">
-        <v>102000</v>
+        <v>74000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-23,000</t>
+          <t>-20,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1809,97 +1809,133 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>頎邦科技</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>頎邦科技</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.38%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>517000</v>
+      </c>
       <c r="K23" t="n">
-        <v>250000</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>390000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-127,000</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-08_00992A_full_holdings.xlsx</t>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.89%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>77000</v>
+      </c>
       <c r="K24" t="n">
-        <v>51000</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>60000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-17,000</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-08_00992A_full_holdings.xlsx</t>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1909,233 +1945,269 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>新代科技</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>新代科技</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>10877000</v>
+        <v>92000</v>
       </c>
       <c r="K25" t="n">
-        <v>11420868</v>
+        <v>80000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>543,868</t>
+          <t>-12,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-08_00992A_full_holdings.xlsx</t>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>南亞電路板</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>南亞電路板</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+        <v>125000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>102000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-23,000</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+          <t>2026-09-08_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>250000</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+          <t>2026-09-08_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3533</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>51000</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+          <t>2026-09-08_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>富喬</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>富喬</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
       <c r="J29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+        <v>10877000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>11420868</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>543,868</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-08_00405A_full_holdings.xlsx</t>
+          <t>2026-09-08_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2157,24 +2229,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>168000</v>
+        <v>1000</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2192,55 +2264,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5.45%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>6.20%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>+0.75%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>1570000</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1720000</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>150,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>2026-09-08_00405A_full_holdings.xlsx</t>
@@ -2255,55 +2309,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>弘塑</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>弘塑</t>
-        </is>
-      </c>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.46%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>1.22%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>152000</v>
-      </c>
-      <c r="K32" t="n">
-        <v>132000</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-20,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>2026-09-08_00405A_full_holdings.xlsx</t>
@@ -2318,55 +2354,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>愛普*</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>愛普*</t>
-        </is>
-      </c>
+          <t>昇陽半導體</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.54%</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>3.44%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>+0.90%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>750000</v>
-      </c>
-      <c r="K33" t="n">
-        <v>950000</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>200,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>2026-09-08_00405A_full_holdings.xlsx</t>
@@ -2376,97 +2394,115 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3131</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>弘塑</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.95%</t>
-        </is>
-      </c>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>91000</v>
-      </c>
+      <c r="J34" t="n">
+        <v>168000</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.71%</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+          <t>5.45%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6.20%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+0.75%</t>
+        </is>
+      </c>
       <c r="J35" t="n">
-        <v>648000</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+        <v>1570000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1720000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>150,000</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2476,60 +2512,60 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>250000</v>
+        <v>152000</v>
       </c>
       <c r="K36" t="n">
-        <v>290000</v>
+        <v>132000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>-20,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2544,48 +2580,48 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.90%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>79000</v>
+        <v>750000</v>
       </c>
       <c r="K37" t="n">
-        <v>109000</v>
+        <v>950000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+          <t>2026-09-08_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2597,56 +2633,272 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>91000</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>648000</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>290000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>+0.50%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>79000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>109000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-08_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>6669</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>3.92%</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>-0.84%</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J42" t="n">
         <v>491644</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K42" t="n">
         <v>421644</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-70,000</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>2026-09-08_00407A_full_holdings.xlsx</t>
         </is>
